--- a/relatorios/Mogo/Itens Vendidos Agendamento/03-2026.xlsx
+++ b/relatorios/Mogo/Itens Vendidos Agendamento/03-2026.xlsx
@@ -57,11 +57,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -452,10 +453,8 @@
           <t>MORANGO - DELICIOSA NAKED F25</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>131,00</t>
-        </is>
+      <c r="B2" s="2" t="n">
+        <v>131</v>
       </c>
     </row>
     <row r="3">
@@ -464,10 +463,8 @@
           <t>MORANGO - DELICIOSA NAKED F20</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>90,00</t>
-        </is>
+      <c r="B3" s="2" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="4">
@@ -476,10 +473,8 @@
           <t>MORANGO - DELICIOSA NAKED F13</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>54,00</t>
-        </is>
+      <c r="B4" s="2" t="n">
+        <v>54</v>
       </c>
     </row>
     <row r="5">
@@ -488,10 +483,8 @@
           <t>TENTACAO F25</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>48,00</t>
-        </is>
+      <c r="B5" s="2" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="6">
@@ -500,10 +493,8 @@
           <t>ALEMA F13</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>30,00</t>
-        </is>
+      <c r="B6" s="2" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="7">
@@ -512,10 +503,8 @@
           <t>QUICHE ALHO PORO F13</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>28,00</t>
-        </is>
+      <c r="B7" s="2" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="8">
@@ -524,10 +513,8 @@
           <t>TENTACAO F13</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>27,00</t>
-        </is>
+      <c r="B8" s="2" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="9">
@@ -536,10 +523,8 @@
           <t>BRIG. C/ MORANGO DARK</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>26,00</t>
-        </is>
+      <c r="B9" s="2" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="10">
@@ -548,10 +533,8 @@
           <t>ALEMA F22</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>25,00</t>
-        </is>
+      <c r="B10" s="2" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="11">
@@ -560,10 +543,8 @@
           <t>BRIG. TRADICIONAL 25UN</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>25,00</t>
-        </is>
+      <c r="B11" s="2" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="12">
@@ -572,10 +553,8 @@
           <t>DELICIA COCO F25</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>24,00</t>
-        </is>
+      <c r="B12" s="2" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="13">
@@ -584,10 +563,8 @@
           <t>CHOCOBERRIES F25</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>23,00</t>
-        </is>
+      <c r="B13" s="2" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="14">
@@ -596,10 +573,8 @@
           <t>TORTINHA BABA</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>23,00</t>
-        </is>
+      <c r="B14" s="2" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="15">
@@ -608,10 +583,8 @@
           <t>BRIG. DARK 25UN</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>22,00</t>
-        </is>
+      <c r="B15" s="2" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="16">
@@ -620,10 +593,8 @@
           <t>BRIG. TESOUROS DE PÁSCOA 12UN</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>21,00</t>
-        </is>
+      <c r="B16" s="2" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="17">
@@ -632,10 +603,8 @@
           <t>CROCANTE F25</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>20,00</t>
-        </is>
+      <c r="B17" s="2" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="18">
@@ -644,10 +613,8 @@
           <t>TORTINHA CHOCOLATE</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>20,00</t>
-        </is>
+      <c r="B18" s="2" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="19">
@@ -656,10 +623,8 @@
           <t>MARAVILHA ABACAXI F25</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>18,00</t>
-        </is>
+      <c r="B19" s="2" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="20">
@@ -668,10 +633,8 @@
           <t>NOVA SWEET DARK F25</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>18,00</t>
-        </is>
+      <c r="B20" s="2" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="21">
@@ -680,10 +643,8 @@
           <t>BRIG. TRADICIONAL 12UN</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>17,00</t>
-        </is>
+      <c r="B21" s="2" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="22">
@@ -692,10 +653,8 @@
           <t>FANTASIA F13</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>16,00</t>
-        </is>
+      <c r="B22" s="2" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="23">
@@ -704,10 +663,8 @@
           <t>FANTASIA F25</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>16,00</t>
-        </is>
+      <c r="B23" s="2" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="24">
@@ -716,10 +673,8 @@
           <t>VELA FAISCA</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>16,00</t>
-        </is>
+      <c r="B24" s="2" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="25">
@@ -728,10 +683,8 @@
           <t>CHOCOBERRIES F20</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>15,00</t>
-        </is>
+      <c r="B25" s="2" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="26">
@@ -740,10 +693,8 @@
           <t>BOLO CENOURA F25</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>14,00</t>
-        </is>
+      <c r="B26" s="2" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="27">
@@ -752,10 +703,8 @@
           <t>EMPADAO FRANGO F25</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>14,00</t>
-        </is>
+      <c r="B27" s="2" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="28">
@@ -764,10 +713,8 @@
           <t>BRIG. NINHO NUTELLA 12UN</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>13,00</t>
-        </is>
+      <c r="B28" s="2" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="29">
@@ -776,10 +723,8 @@
           <t>BOLO LARANJA F25</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>11,00</t>
-        </is>
+      <c r="B29" s="2" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="30">
@@ -788,10 +733,8 @@
           <t>BRIG. DOIS AMORES 12UN</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>11,00</t>
-        </is>
+      <c r="B30" s="2" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="31">
@@ -800,10 +743,8 @@
           <t>QUICHE ALHO PORO F25</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>11,00</t>
-        </is>
+      <c r="B31" s="2" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="32">
@@ -812,10 +753,8 @@
           <t>RED VELVET F20</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>11,00</t>
-        </is>
+      <c r="B32" s="2" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="33">
@@ -824,10 +763,8 @@
           <t>TORTA MOUSSE F13</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>11,00</t>
-        </is>
+      <c r="B33" s="2" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="34">
@@ -836,10 +773,8 @@
           <t>BRIG. MIX 25UN</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>10,00</t>
-        </is>
+      <c r="B34" s="2" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="35">
@@ -848,10 +783,8 @@
           <t>EMILIA F25</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>10,00</t>
-        </is>
+      <c r="B35" s="2" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="36">
@@ -860,10 +793,8 @@
           <t>QUICHE CEBOLA F13</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>10,00</t>
-        </is>
+      <c r="B36" s="2" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="37">
@@ -872,10 +803,8 @@
           <t>RED VELVET F25</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>10,00</t>
-        </is>
+      <c r="B37" s="2" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="38">
@@ -884,10 +813,8 @@
           <t>TORTINHA GOURMET BABA FESTA CX</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>10,00</t>
-        </is>
+      <c r="B38" s="2" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="39">
@@ -896,10 +823,8 @@
           <t>BRIG. BRULLE 12UN</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>9,00</t>
-        </is>
+      <c r="B39" s="2" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="40">
@@ -908,10 +833,8 @@
           <t>BRIG. MIX 12UN</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>9,00</t>
-        </is>
+      <c r="B40" s="2" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="41">
@@ -920,10 +843,8 @@
           <t>TORTA LIMAO F25</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>9,00</t>
-        </is>
+      <c r="B41" s="2" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="42">
@@ -932,10 +853,8 @@
           <t>AURORA F25</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>8,00</t>
-        </is>
+      <c r="B42" s="2" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="43">
@@ -944,10 +863,8 @@
           <t>BRIG. C/ MORANGO TRADICIONAL</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>8,00</t>
-        </is>
+      <c r="B43" s="2" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="44">
@@ -956,10 +873,8 @@
           <t>BRIG. DOIS AMORES 25UN</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>8,00</t>
-        </is>
+      <c r="B44" s="2" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="45">
@@ -968,10 +883,8 @@
           <t>CHEESECAKE F. VERM F25</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>8,00</t>
-        </is>
+      <c r="B45" s="2" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="46">
@@ -980,10 +893,8 @@
           <t>DELICIA CAMADAS F13</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>8,00</t>
-        </is>
+      <c r="B46" s="2" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="47">
@@ -992,10 +903,8 @@
           <t>DELICIA COCO F13</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>8,00</t>
-        </is>
+      <c r="B47" s="2" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="48">
@@ -1004,10 +913,8 @@
           <t>EMPADAO FRANGO F13</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>8,00</t>
-        </is>
+      <c r="B48" s="2" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="49">
@@ -1016,10 +923,8 @@
           <t>MARAVILHA ABACAXI F13</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>8,00</t>
-        </is>
+      <c r="B49" s="2" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="50">
@@ -1028,10 +933,8 @@
           <t>MORANGO - FT DELICIOSA</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>8,00</t>
-        </is>
+      <c r="B50" s="2" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="51">
@@ -1040,10 +943,8 @@
           <t>PET HAPPY</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>8,00</t>
-        </is>
+      <c r="B51" s="2" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="52">
@@ -1052,10 +953,8 @@
           <t>BANOFFE F20</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>7,00</t>
-        </is>
+      <c r="B52" s="2" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="53">
@@ -1064,10 +963,8 @@
           <t>BRIG. PRETO PRECIOSO 12UN</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>7,00</t>
-        </is>
+      <c r="B53" s="2" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="54">
@@ -1076,10 +973,8 @@
           <t>CHOCOBERRIES F13</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>7,00</t>
-        </is>
+      <c r="B54" s="2" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="55">
@@ -1088,10 +983,8 @@
           <t>COCA COLA ZERO</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>7,00</t>
-        </is>
+      <c r="B55" s="2" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="56">
@@ -1100,10 +993,8 @@
           <t>BRIG. BEIJINHO 25UN</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>6,00</t>
-        </is>
+      <c r="B56" s="2" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="57">
@@ -1112,10 +1003,8 @@
           <t>BRIG. BRULLE 25UN</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>6,00</t>
-        </is>
+      <c r="B57" s="2" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="58">
@@ -1124,10 +1013,8 @@
           <t>BRIG. DARK 12UN</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>6,00</t>
-        </is>
+      <c r="B58" s="2" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="59">
@@ -1136,10 +1023,8 @@
           <t>BRIG. NINHO NUTELLA 25UN</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>6,00</t>
-        </is>
+      <c r="B59" s="2" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="60">
@@ -1148,10 +1033,8 @@
           <t>DELICIA CAMADAS F25</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>6,00</t>
-        </is>
+      <c r="B60" s="2" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="61">
@@ -1160,10 +1043,8 @@
           <t>EMILIA F13</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>6,00</t>
-        </is>
+      <c r="B61" s="2" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="62">
@@ -1172,10 +1053,8 @@
           <t>NOVA SWEET DARK F13</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>6,00</t>
-        </is>
+      <c r="B62" s="2" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="63">
@@ -1184,10 +1063,8 @@
           <t>TORTA MOUSSE F25</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>6,00</t>
-        </is>
+      <c r="B63" s="2" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="64">
@@ -1196,10 +1073,8 @@
           <t>VELA DOURADA NUMERO - 1</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>6,00</t>
-        </is>
+      <c r="B64" s="2" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="65">
@@ -1208,10 +1083,8 @@
           <t>BRIG. CHURROS 12UN</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>5,00</t>
-        </is>
+      <c r="B65" s="2" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="66">
@@ -1220,10 +1093,8 @@
           <t>BRIG. CHURROS 25UN</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>5,00</t>
-        </is>
+      <c r="B66" s="2" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="67">
@@ -1232,10 +1103,8 @@
           <t>QUICHE CEBOLA F25</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>5,00</t>
-        </is>
+      <c r="B67" s="2" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="68">
@@ -1244,10 +1113,8 @@
           <t>QUICHE PRESUNTO F13</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>5,00</t>
-        </is>
+      <c r="B68" s="2" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="69">
@@ -1256,10 +1123,8 @@
           <t>QUICHE PRESUNTO F25</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>5,00</t>
-        </is>
+      <c r="B69" s="2" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="70">
@@ -1268,10 +1133,8 @@
           <t>Taxa de Serviço</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>5,00</t>
-        </is>
+      <c r="B70" s="2" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="71">
@@ -1280,10 +1143,8 @@
           <t>TORTA BANANA F13</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>5,00</t>
-        </is>
+      <c r="B71" s="2" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="72">
@@ -1292,10 +1153,8 @@
           <t>TORTA COLORIDA F25</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>5,00</t>
-        </is>
+      <c r="B72" s="2" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="73">
@@ -1304,10 +1163,8 @@
           <t>TORTA LIMAO F13</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>5,00</t>
-        </is>
+      <c r="B73" s="2" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="74">
@@ -1316,10 +1173,8 @@
           <t>VELA CORACAO 4UN</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>5,00</t>
-        </is>
+      <c r="B74" s="2" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="75">
@@ -1328,10 +1183,8 @@
           <t>VELA DOURADA NUMERO - 9</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>5,00</t>
-        </is>
+      <c r="B75" s="2" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="76">
@@ -1340,10 +1193,8 @@
           <t>VELA DOURADA NUMERO - X</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>5,00</t>
-        </is>
+      <c r="B76" s="2" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="77">
@@ -1352,10 +1203,8 @@
           <t>VELA ESPIRAL FINA ROSE 4UN</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>5,00</t>
-        </is>
+      <c r="B77" s="2" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="78">
@@ -1364,10 +1213,8 @@
           <t>VELA PRATA NUMERO - 0</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>5,00</t>
-        </is>
+      <c r="B78" s="2" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="79">
@@ -1376,10 +1223,8 @@
           <t>VULCAO CENOURA</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>5,00</t>
-        </is>
+      <c r="B79" s="2" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="80">
@@ -1388,10 +1233,8 @@
           <t>AURORA ENFEITADA F25</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>4,00</t>
-        </is>
+      <c r="B80" s="2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="81">
@@ -1400,10 +1243,8 @@
           <t>BANOFFE F13</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>4,00</t>
-        </is>
+      <c r="B81" s="2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="82">
@@ -1412,10 +1253,8 @@
           <t>BOLO TOCA DO COELHO</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>4,00</t>
-        </is>
+      <c r="B82" s="2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="83">
@@ -1424,10 +1263,8 @@
           <t>BRIG. BRANCO DIVERTIDO 12UN</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>4,00</t>
-        </is>
+      <c r="B83" s="2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="84">
@@ -1436,10 +1273,8 @@
           <t>BRIG. COCO QUEIMADO 12UN</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>4,00</t>
-        </is>
+      <c r="B84" s="2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="85">
@@ -1448,10 +1283,8 @@
           <t>BRIG. PINGO DE EMILIA 25UN</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>4,00</t>
-        </is>
+      <c r="B85" s="2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="86">
@@ -1460,10 +1293,8 @@
           <t>BRIG. PRETO PRECIOSO 25UN</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>4,00</t>
-        </is>
+      <c r="B86" s="2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="87">
@@ -1472,10 +1303,8 @@
           <t>CROCANTE F13</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>4,00</t>
-        </is>
+      <c r="B87" s="2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="88">
@@ -1484,10 +1313,8 @@
           <t>FT ALEMA</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>4,00</t>
-        </is>
+      <c r="B88" s="2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="89">
@@ -1496,10 +1323,8 @@
           <t>FT EMPADAO FRANGO</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>4,00</t>
-        </is>
+      <c r="B89" s="2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="90">
@@ -1508,10 +1333,8 @@
           <t>MERENGUE 200ML</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>4,00</t>
-        </is>
+      <c r="B90" s="2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="91">
@@ -1520,10 +1343,8 @@
           <t>PAO DE QUEIJO</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>4,00</t>
-        </is>
+      <c r="B91" s="2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="92">
@@ -1532,10 +1353,8 @@
           <t>PATE SECRETO 150GR</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>4,00</t>
-        </is>
+      <c r="B92" s="2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="93">
@@ -1544,10 +1363,8 @@
           <t>QUEBRA NOZES F13</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>4,00</t>
-        </is>
+      <c r="B93" s="2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="94">
@@ -1556,10 +1373,8 @@
           <t>RED VELVET F13</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>4,00</t>
-        </is>
+      <c r="B94" s="2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="95">
@@ -1568,10 +1383,8 @@
           <t>AURORA F13</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>3,00</t>
-        </is>
+      <c r="B95" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="96">
@@ -1580,10 +1393,8 @@
           <t>BISC PALMIER 100GR</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>3,00</t>
-        </is>
+      <c r="B96" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="97">
@@ -1592,10 +1403,8 @@
           <t>BRIG. BEIJINHO 12UN</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>3,00</t>
-        </is>
+      <c r="B97" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="98">
@@ -1604,10 +1413,8 @@
           <t>BRIG. BRANCO DIVERTIDO 25UN</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>3,00</t>
-        </is>
+      <c r="B98" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="99">
@@ -1616,10 +1423,8 @@
           <t>BRIG. COCO QUEIMADO 25UN</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>3,00</t>
-        </is>
+      <c r="B99" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="100">
@@ -1628,10 +1433,8 @@
           <t>CHEESECAKE MORANGO F25</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>3,00</t>
-        </is>
+      <c r="B100" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="101">
@@ -1640,10 +1443,8 @@
           <t>CHOCONOZES F13</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>3,00</t>
-        </is>
+      <c r="B101" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="102">
@@ -1652,10 +1453,8 @@
           <t>FIOS DE OVOS 250GRS</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>3,00</t>
-        </is>
+      <c r="B102" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="103">
@@ -1664,10 +1463,8 @@
           <t>FT MARAVILHA ABACAXI</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>3,00</t>
-        </is>
+      <c r="B103" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="104">
@@ -1676,10 +1473,8 @@
           <t>FT SWEET DARK</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>3,00</t>
-        </is>
+      <c r="B104" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="105">
@@ -1688,10 +1483,8 @@
           <t>FT TENTACAO</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>3,00</t>
-        </is>
+      <c r="B105" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="106">
@@ -1700,10 +1493,8 @@
           <t>QUINDIM UN</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>3,00</t>
-        </is>
+      <c r="B106" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="107">
@@ -1712,10 +1503,8 @@
           <t>SALADA VERAO</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>3,00</t>
-        </is>
+      <c r="B107" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="108">
@@ -1724,10 +1513,8 @@
           <t>TORTA BANANA F22</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>3,00</t>
-        </is>
+      <c r="B108" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="109">
@@ -1736,10 +1523,8 @@
           <t>TORTA CAÇA AO CHOCOLATE F13</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>3,00</t>
-        </is>
+      <c r="B109" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -1748,10 +1533,8 @@
           <t>TORTA CAÇA AO CHOCOLATE F25</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>3,00</t>
-        </is>
+      <c r="B110" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="111">
@@ -1760,10 +1543,8 @@
           <t>TORTINHA GOURMET MISTA FESTA CX</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>3,00</t>
-        </is>
+      <c r="B111" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="112">
@@ -1772,10 +1553,8 @@
           <t>VELA DOURADA NUMERO - 2</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>3,00</t>
-        </is>
+      <c r="B112" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="113">
@@ -1784,10 +1563,8 @@
           <t>VELA DOURADA NUMERO - 4</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>3,00</t>
-        </is>
+      <c r="B113" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="114">
@@ -1796,10 +1573,8 @@
           <t>VELA DOURADA NUMERO - 7</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>3,00</t>
-        </is>
+      <c r="B114" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="115">
@@ -1808,10 +1583,8 @@
           <t>BRIG. CARAMELO 12UN</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>2,00</t>
-        </is>
+      <c r="B115" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="116">
@@ -1820,10 +1593,8 @@
           <t>BRIG. CHOCOLATE BRANCO 12UN</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>2,00</t>
-        </is>
+      <c r="B116" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="117">
@@ -1832,10 +1603,8 @@
           <t>BRIG. CHOCOLATE BRANCO 25UN</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>2,00</t>
-        </is>
+      <c r="B117" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="118">
@@ -1844,10 +1613,8 @@
           <t>BRIG. NOZES 12UN</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>2,00</t>
-        </is>
+      <c r="B118" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="119">
@@ -1856,10 +1623,8 @@
           <t>BRIG. PINGO DE EMILIA 12UN</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>2,00</t>
-        </is>
+      <c r="B119" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="120">
@@ -1868,10 +1633,8 @@
           <t>CHEESECAKE GOIABA F25</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>2,00</t>
-        </is>
+      <c r="B120" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="121">
@@ -1880,10 +1643,8 @@
           <t>CHEESECAKE MORANGO F13</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>2,00</t>
-        </is>
+      <c r="B121" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="122">
@@ -1892,10 +1653,8 @@
           <t>FESTIVA - DELICIA DE COCO F25</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>2,00</t>
-        </is>
+      <c r="B122" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="123">
@@ -1904,10 +1663,8 @@
           <t>FT CHOCOBERRIES</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>2,00</t>
-        </is>
+      <c r="B123" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="124">
@@ -1916,10 +1673,8 @@
           <t>FT COLORIDA</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>2,00</t>
-        </is>
+      <c r="B124" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="125">
@@ -1928,10 +1683,8 @@
           <t>FT FANTASIA</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>2,00</t>
-        </is>
+      <c r="B125" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="126">
@@ -1940,10 +1693,8 @@
           <t>GELEIA MORANGO 200GR</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>2,00</t>
-        </is>
+      <c r="B126" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="127">
@@ -1952,10 +1703,8 @@
           <t>MORANGO - DELICIOSA NAKED F30</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>2,00</t>
-        </is>
+      <c r="B127" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="128">
@@ -1964,10 +1713,8 @@
           <t>OVO NINHO E NUTELLA</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>2,00</t>
-        </is>
+      <c r="B128" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="129">
@@ -1976,10 +1723,8 @@
           <t>SALADA MONTADA</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>2,00</t>
-        </is>
+      <c r="B129" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="130">
@@ -1988,10 +1733,8 @@
           <t>TORTINHA GOURMET CHOCO FESTA CX</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>2,00</t>
-        </is>
+      <c r="B130" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="131">
@@ -2000,10 +1743,8 @@
           <t>VELA DOURADA NUMERO - 6</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>2,00</t>
-        </is>
+      <c r="B131" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="132">
@@ -2012,10 +1753,8 @@
           <t>VELA DOURADA NUMERO - 8</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>2,00</t>
-        </is>
+      <c r="B132" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="133">
@@ -2024,10 +1763,8 @@
           <t>VELA VULCAO DOURADA</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>2,00</t>
-        </is>
+      <c r="B133" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="134">
@@ -2036,10 +1773,8 @@
           <t>ALEMA F30</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>1,00</t>
-        </is>
+      <c r="B134" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="135">
@@ -2048,10 +1783,8 @@
           <t>AURORA ENFEITADA F13</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>1,00</t>
-        </is>
+      <c r="B135" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="136">
@@ -2060,10 +1793,8 @@
           <t>BISC COOKIE SUICO 100GR</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>1,00</t>
-        </is>
+      <c r="B136" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="137">
@@ -2072,10 +1803,8 @@
           <t>BISC GOIABINHA 100GR</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>1,00</t>
-        </is>
+      <c r="B137" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="138">
@@ -2084,10 +1813,8 @@
           <t>BISC GORGONZOLA 100GR</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>1,00</t>
-        </is>
+      <c r="B138" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="139">
@@ -2096,10 +1823,8 @@
           <t>BISC QUEIJO PARMESAO 100GR</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>1,00</t>
-        </is>
+      <c r="B139" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="140">
@@ -2108,10 +1833,8 @@
           <t>BOLO INGLES NOITE DE PÁSCOA</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>1,00</t>
-        </is>
+      <c r="B140" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="141">
@@ -2120,10 +1843,8 @@
           <t>BOLO MILHO COM COCO F25</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>1,00</t>
-        </is>
+      <c r="B141" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="142">
@@ -2132,10 +1853,8 @@
           <t>BRIG. BRANCO PRECIOSO 25UN</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>1,00</t>
-        </is>
+      <c r="B142" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="143">
@@ -2144,10 +1863,8 @@
           <t>BRIG. C/ MORANGO BRULEE</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>1,00</t>
-        </is>
+      <c r="B143" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="144">
@@ -2156,10 +1873,8 @@
           <t>BRIG. CARAMELO 25UN</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>1,00</t>
-        </is>
+      <c r="B144" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="145">
@@ -2168,10 +1883,8 @@
           <t>BRIG. NOZES 25UN</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>1,00</t>
-        </is>
+      <c r="B145" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="146">
@@ -2180,10 +1893,8 @@
           <t>CALDA CHOC 200GR</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>1,00</t>
-        </is>
+      <c r="B146" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="147">
@@ -2192,10 +1903,8 @@
           <t>CALDA LARANJA 200GR</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>1,00</t>
-        </is>
+      <c r="B147" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="148">
@@ -2204,10 +1913,8 @@
           <t>CHEESECAKE DAMASCO F25</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>1,00</t>
-        </is>
+      <c r="B148" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="149">
@@ -2216,10 +1923,8 @@
           <t>CHEESECAKE F. VERM F13</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>1,00</t>
-        </is>
+      <c r="B149" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -2228,10 +1933,8 @@
           <t>CHEESECAKE GOIABA F13</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>1,00</t>
-        </is>
+      <c r="B150" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="151">
@@ -2240,10 +1943,8 @@
           <t>COCA COLA</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>1,00</t>
-        </is>
+      <c r="B151" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="152">
@@ -2252,10 +1953,8 @@
           <t>ENCHARCADA COPO 180gr</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>1,00</t>
-        </is>
+      <c r="B152" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="153">
@@ -2264,10 +1963,8 @@
           <t>ENCHARCADA F13</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>1,00</t>
-        </is>
+      <c r="B153" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="154">
@@ -2276,10 +1973,8 @@
           <t>FT AURORA</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>1,00</t>
-        </is>
+      <c r="B154" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="155">
@@ -2288,10 +1983,8 @@
           <t>FT BOLO MILHO</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>1,00</t>
-        </is>
+      <c r="B155" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="156">
@@ -2300,10 +1993,8 @@
           <t>FT CROCANTE</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>1,00</t>
-        </is>
+      <c r="B156" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="157">
@@ -2312,10 +2003,8 @@
           <t>FT DELICIA COCO</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>1,00</t>
-        </is>
+      <c r="B157" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="158">
@@ -2324,10 +2013,8 @@
           <t>FT ROCAMBOLE LARANJA</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>1,00</t>
-        </is>
+      <c r="B158" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="159">
@@ -2336,10 +2023,8 @@
           <t>FT TORTA BANANA</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>1,00</t>
-        </is>
+      <c r="B159" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="160">
@@ -2348,10 +2033,8 @@
           <t>FT TORTA MOUSSE</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>1,00</t>
-        </is>
+      <c r="B160" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="161">
@@ -2360,10 +2043,8 @@
           <t>IF BRIG. DOIS AMORES</t>
         </is>
       </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>1,00</t>
-        </is>
+      <c r="B161" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="162">
@@ -2372,10 +2053,8 @@
           <t>MISTO PAO FRANCES</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>1,00</t>
-        </is>
+      <c r="B162" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="163">
@@ -2384,10 +2063,8 @@
           <t>QUEBRA NOZES F25</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>1,00</t>
-        </is>
+      <c r="B163" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="164">
@@ -2396,10 +2073,8 @@
           <t>VELA DOURADA NUMERO - 0</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>1,00</t>
-        </is>
+      <c r="B164" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="165">
@@ -2408,10 +2083,8 @@
           <t>VELA DOURADA NUMERO - 3</t>
         </is>
       </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>1,00</t>
-        </is>
+      <c r="B165" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="166">
@@ -2420,10 +2093,8 @@
           <t>VELA DOURADA NUMERO - 5</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>1,00</t>
-        </is>
+      <c r="B166" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="167">
@@ -2432,10 +2103,8 @@
           <t>VELA ESTRELA DOURADA 4UN</t>
         </is>
       </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>1,00</t>
-        </is>
+      <c r="B167" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="168">
@@ -2444,10 +2113,8 @@
           <t>VELA PARABENS NEON</t>
         </is>
       </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>1,00</t>
-        </is>
+      <c r="B168" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="169">
@@ -2456,10 +2123,8 @@
           <t>VELA PRATA NUMERO - 1</t>
         </is>
       </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>1,00</t>
-        </is>
+      <c r="B169" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="170">
@@ -2468,10 +2133,8 @@
           <t>VELA PRATA NUMERO - 3</t>
         </is>
       </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>1,00</t>
-        </is>
+      <c r="B170" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="171">
@@ -2480,10 +2143,8 @@
           <t>VELA PRATA NUMERO - X</t>
         </is>
       </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>1,00</t>
-        </is>
+      <c r="B171" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="172">
@@ -2492,12 +2153,11 @@
           <t>VULCAO DIVERTIDO</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>1,00</t>
-        </is>
-      </c>
-    </row>
+      <c r="B172" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173"/>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
